--- a/ПУ3/Модуль 1/Прил_2_ОЗ_КОД 09.02.07-2-2026-М1/import/12OrderInfo.xlsx
+++ b/ПУ3/Модуль 1/Прил_2_ОЗ_КОД 09.02.07-2-2026-М1/import/12OrderInfo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Study\МДК.04.02(Кретинин)\demka4\ПУ3\Модуль 1\Прил_2_ОЗ_КОД 09.02.07-2-2026-М1\import\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C457592-A4D7-423C-A310-B0804067070F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC87730F-0387-4137-97A8-EEEEC07DC834}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11295" yWindow="4065" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
